--- a/Assets/Resources/MasterData/ItemDropTable.xlsx
+++ b/Assets/Resources/MasterData/ItemDropTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B96D43E-BDB9-49D8-AC78-927254A1626B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD17B6C-4670-4B18-8E09-D94325D03FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12330" yWindow="-13635" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10155" yWindow="-13935" windowWidth="12390" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDropTable" sheetId="1" r:id="rId1"/>
@@ -445,7 +445,7 @@
         <v>101</v>
       </c>
       <c r="F2" s="2">
-        <v>-1</v>
+        <v>203</v>
       </c>
       <c r="G2" s="2">
         <v>-1</v>
@@ -474,7 +474,7 @@
         <v>301</v>
       </c>
       <c r="F3" s="2">
-        <v>-1</v>
+        <v>203</v>
       </c>
       <c r="G3" s="2">
         <v>-1</v>
@@ -491,10 +491,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>-1</v>
+        <v>203</v>
       </c>
       <c r="C4" s="2">
-        <v>-1</v>
+        <v>201</v>
       </c>
       <c r="D4" s="2">
         <v>-1</v>

--- a/Assets/Resources/MasterData/ItemDropTable.xlsx
+++ b/Assets/Resources/MasterData/ItemDropTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD17B6C-4670-4B18-8E09-D94325D03FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAA8757-B528-41DA-B7FC-3C38366CBA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10155" yWindow="-13935" windowWidth="12390" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2025" yWindow="-13125" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDropTable" sheetId="1" r:id="rId1"/>
@@ -439,13 +439,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>100</v>
+        <v>-1</v>
       </c>
       <c r="E2" s="2">
-        <v>101</v>
+        <v>-1</v>
       </c>
       <c r="F2" s="2">
-        <v>203</v>
+        <v>-1</v>
       </c>
       <c r="G2" s="2">
         <v>-1</v>

--- a/Assets/Resources/MasterData/ItemDropTable.xlsx
+++ b/Assets/Resources/MasterData/ItemDropTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAA8757-B528-41DA-B7FC-3C38366CBA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CFF979-58CA-464C-91F9-DAE54792BE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="-13125" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3705" yWindow="-13590" windowWidth="16995" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDropTable" sheetId="1" r:id="rId1"/>
@@ -468,13 +468,13 @@
         <v>200</v>
       </c>
       <c r="D3" s="2">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E3" s="2">
-        <v>301</v>
+        <v>-1</v>
       </c>
       <c r="F3" s="2">
-        <v>203</v>
+        <v>-1</v>
       </c>
       <c r="G3" s="2">
         <v>-1</v>
@@ -494,7 +494,7 @@
         <v>203</v>
       </c>
       <c r="C4" s="2">
-        <v>201</v>
+        <v>600</v>
       </c>
       <c r="D4" s="2">
         <v>-1</v>
